--- a/outputs/04_individual_models/mmse_results.xlsx
+++ b/outputs/04_individual_models/mmse_results.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1057" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="96">
   <si>
     <t>RID</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>incorrect-low</t>
+  </si>
+  <si>
+    <t>outcome</t>
   </si>
   <si>
     <t>HIGH_conf(&gt;=0.8)</t>
@@ -6758,16 +6761,19 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="B1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>15</v>
+      <c r="A2" t="s">
+        <v>16</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6777,8 +6783,8 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>16</v>
+      <c r="A3" t="s">
+        <v>17</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -6799,15 +6805,15 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B2">
         <v>233</v>
@@ -6815,7 +6821,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3">
         <v>0.6909999999999999</v>
@@ -6823,7 +6829,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4">
         <v>0.6395</v>
@@ -6831,7 +6837,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B5">
         <v>0.0515</v>
@@ -6839,7 +6845,7 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B6">
         <v>0.6823</v>
@@ -6847,7 +6853,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B7">
         <v>0.5717</v>
@@ -6855,7 +6861,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B8">
         <v>0.3605</v>
@@ -6863,7 +6869,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>0.5844</v>
@@ -6871,7 +6877,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10">
         <v>0.2024</v>
@@ -6879,7 +6885,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B11">
         <v>0.9664</v>
@@ -6887,7 +6893,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B12">
         <v>0.7727000000000001</v>
@@ -6895,7 +6901,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B13">
         <v>0.3208</v>
@@ -6903,7 +6909,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B14">
         <v>17</v>
@@ -6911,7 +6917,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>5</v>
@@ -6919,7 +6925,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16">
         <v>67</v>
@@ -6927,7 +6933,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17">
         <v>144</v>
@@ -6935,12 +6941,12 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B19">
         <v>0.6909999999999999</v>
@@ -6948,7 +6954,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -6956,7 +6962,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -6964,7 +6970,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B22">
         <v>0.6309</v>
@@ -6972,7 +6978,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B23">
         <v>0.7511</v>
@@ -6980,7 +6986,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24">
         <v>0.6064000000000001</v>
@@ -6988,7 +6994,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25">
         <v>0.7529</v>
@@ -6996,7 +7002,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26">
         <v>16</v>
@@ -7004,7 +7010,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27">
         <v>37</v>
@@ -7012,7 +7018,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28">
         <v>9</v>
@@ -7020,7 +7026,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29">
         <v>-0.5823</v>
@@ -7038,16 +7044,16 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7055,13 +7061,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2">
         <v>-0.166036</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7069,13 +7075,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C3">
         <v>-0.154364</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7083,13 +7089,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C4">
         <v>-0.104646</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7097,13 +7103,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C5">
         <v>-0.08735</v>
       </c>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7111,13 +7117,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>-0.08389099999999999</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7125,13 +7131,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>-0.063719</v>
       </c>
       <c r="D7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7139,13 +7145,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8">
         <v>-0.03563</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7153,13 +7159,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C9">
         <v>-0.033578</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7167,13 +7173,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C10">
         <v>-0.017784</v>
       </c>
       <c r="D10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7181,13 +7187,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -7195,13 +7201,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -7209,13 +7215,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -7223,13 +7229,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -7237,13 +7243,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -7251,13 +7257,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -7265,13 +7271,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -7279,13 +7285,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -7293,13 +7299,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -7307,13 +7313,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -7321,13 +7327,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -7335,13 +7341,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -7349,13 +7355,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -7363,13 +7369,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -7377,13 +7383,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -7391,13 +7397,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -7405,13 +7411,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -7419,13 +7425,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -7433,13 +7439,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -7447,13 +7453,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -7461,13 +7467,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -7475,13 +7481,13 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -7489,13 +7495,13 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -7503,13 +7509,13 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -7517,13 +7523,13 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -7531,13 +7537,13 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -7545,13 +7551,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -7559,13 +7565,13 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -7580,19 +7586,19 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:5">
